--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N23_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.7179809592655</v>
+        <v>2.554171905880644</v>
       </c>
       <c r="D2" t="n">
-        <v>15.91983708085057</v>
+        <v>2.586973525638218</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
